--- a/outputs/per-fund/vc-investments-paradigm.xlsx
+++ b/outputs/per-fund/vc-investments-paradigm.xlsx
@@ -723,7 +723,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Only Paradigm. The full overview with all twenty funds is in vc-investments-full.xlsx.</t>
+          <t>Only Paradigm. The full overview with all 59 funds is in vc-investments-full.xlsx.</t>
         </is>
       </c>
     </row>
@@ -879,7 +879,7 @@
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>The twenty funds, with control totals per external source.</t>
+          <t>The 59 funds, with control totals per external source.</t>
         </is>
       </c>
     </row>
@@ -915,7 +915,7 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>One row per company in which at least one of the twenty funds invested.</t>
+          <t>One row per company in which at least one of these 59 funds invested.</t>
         </is>
       </c>
     </row>
@@ -20200,11 +20200,11 @@
         <v>1</v>
       </c>
       <c r="K2" s="6" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="L2" s="5" t="inlineStr">
         <is>
-          <t>coinbase-ventures, dragonfly, electric-capital, paradigm, polychain</t>
+          <t>1kx, arrington-capital, coinbase-ventures, dragonfly, electric-capital, paradigm, polychain</t>
         </is>
       </c>
       <c r="M2" s="7" t="inlineStr">
@@ -20263,11 +20263,11 @@
         <v>2</v>
       </c>
       <c r="K3" s="6" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L3" s="5" t="inlineStr">
         <is>
-          <t>coinbase-ventures, founders-fund, multicoin-capital, pantera, paradigm, semantic-ventures</t>
+          <t>coinbase-ventures, founders-fund, multicoin-capital, pantera, paradigm, semantic-ventures, sequoia-capital</t>
         </is>
       </c>
       <c r="M3" s="7" t="inlineStr">
@@ -20322,11 +20322,11 @@
         <v>2</v>
       </c>
       <c r="K4" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L4" s="5" t="inlineStr">
         <is>
-          <t>multicoin-capital, pantera, paradigm</t>
+          <t>multicoin-capital, pantera, paradigm, sequoia-capital</t>
         </is>
       </c>
       <c r="M4" s="7" t="inlineStr">
@@ -20877,11 +20877,11 @@
         <v>2</v>
       </c>
       <c r="K13" s="6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L13" s="5" t="inlineStr">
         <is>
-          <t>coinbase-ventures, dragonfly, pantera, paradigm, polychain</t>
+          <t>coinbase-ventures, dragonfly, fenbushi-capital, pantera, paradigm, polychain</t>
         </is>
       </c>
       <c r="M13" s="7" t="inlineStr">
@@ -20999,11 +20999,11 @@
         <v>1</v>
       </c>
       <c r="K15" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L15" s="5" t="inlineStr">
         <is>
-          <t>paradigm</t>
+          <t>fenbushi-capital, paradigm</t>
         </is>
       </c>
       <c r="M15" s="7" t="inlineStr">
@@ -21245,11 +21245,11 @@
         <v>0</v>
       </c>
       <c r="K19" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L19" s="5" t="inlineStr">
         <is>
-          <t>a16z-crypto, paradigm</t>
+          <t>a16z-crypto, paradigm, parafi-capital</t>
         </is>
       </c>
       <c r="M19" s="7" t="inlineStr">
@@ -21308,11 +21308,11 @@
         <v>1</v>
       </c>
       <c r="K20" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L20" s="5" t="inlineStr">
         <is>
-          <t>bain-capital-crypto, paradigm</t>
+          <t>bain-capital-crypto, hack-vc, paradigm</t>
         </is>
       </c>
       <c r="M20" s="7" t="inlineStr">
@@ -21371,11 +21371,11 @@
         <v>1</v>
       </c>
       <c r="K21" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L21" s="5" t="inlineStr">
         <is>
-          <t>bain-capital-crypto, dragonfly, paradigm</t>
+          <t>bain-capital-crypto, dragonfly, hack-vc, paradigm</t>
         </is>
       </c>
       <c r="M21" s="7" t="inlineStr">
@@ -21493,11 +21493,11 @@
         <v>1</v>
       </c>
       <c r="K23" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L23" s="5" t="inlineStr">
         <is>
-          <t>paradigm</t>
+          <t>digital-currency-group, galaxy-digital, paradigm</t>
         </is>
       </c>
       <c r="M23" s="7" t="inlineStr">
@@ -21556,11 +21556,11 @@
         <v>2</v>
       </c>
       <c r="K24" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L24" s="5" t="inlineStr">
         <is>
-          <t>paradigm</t>
+          <t>paradigm, sequoia-capital</t>
         </is>
       </c>
       <c r="M24" s="7" t="inlineStr">
@@ -21741,11 +21741,11 @@
         <v>0</v>
       </c>
       <c r="K27" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L27" s="5" t="inlineStr">
         <is>
-          <t>coinbase-ventures, paradigm</t>
+          <t>coinbase-ventures, iosg-ventures, paradigm</t>
         </is>
       </c>
       <c r="M27" s="7" t="inlineStr">
@@ -21867,11 +21867,11 @@
         <v>2</v>
       </c>
       <c r="K29" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L29" s="5" t="inlineStr">
         <is>
-          <t>coinbase-ventures, paradigm</t>
+          <t>coinbase-ventures, galaxy-digital, paradigm</t>
         </is>
       </c>
       <c r="M29" s="7" t="inlineStr">
@@ -21993,11 +21993,11 @@
         <v>3</v>
       </c>
       <c r="K31" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L31" s="5" t="inlineStr">
         <is>
-          <t>paradigm</t>
+          <t>galaxy-digital, paradigm</t>
         </is>
       </c>
       <c r="M31" s="7" t="inlineStr">
@@ -22056,11 +22056,11 @@
         <v>1</v>
       </c>
       <c r="K32" s="6" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L32" s="5" t="inlineStr">
         <is>
-          <t>founders-fund, pantera, paradigm</t>
+          <t>alameda-research, founders-fund, pantera, paradigm, sequoia-capital</t>
         </is>
       </c>
       <c r="M32" s="7" t="inlineStr">
@@ -22115,11 +22115,11 @@
         <v>1</v>
       </c>
       <c r="K33" s="6" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="L33" s="5" t="inlineStr">
         <is>
-          <t>coinbase-ventures, delphi-ventures, dragonfly, paradigm, robot-ventures</t>
+          <t>alameda-research, coinbase-ventures, delphi-ventures, digital-currency-group, dragonfly, paradigm, robot-ventures</t>
         </is>
       </c>
       <c r="M33" s="7" t="inlineStr">
@@ -22302,11 +22302,11 @@
         <v>1</v>
       </c>
       <c r="K36" s="6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L36" s="5" t="inlineStr">
         <is>
-          <t>framework-ventures, paradigm</t>
+          <t>alliance-dao, cms-holdings, framework-ventures, paradigm</t>
         </is>
       </c>
       <c r="M36" s="7" t="inlineStr">
@@ -22365,11 +22365,11 @@
         <v>1</v>
       </c>
       <c r="K37" s="6" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="L37" s="5" t="inlineStr">
         <is>
-          <t>a16z-crypto, delphi-ventures, electric-capital, paradigm, polychain</t>
+          <t>a16z-crypto, cms-holdings, cmt-digital, delphi-ventures, electric-capital, hashkey-capital, paradigm, polychain</t>
         </is>
       </c>
       <c r="M37" s="7" t="inlineStr">
@@ -22428,11 +22428,11 @@
         <v>0</v>
       </c>
       <c r="K38" s="6" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L38" s="5" t="inlineStr">
         <is>
-          <t>coinbase-ventures, multicoin-capital, paradigm</t>
+          <t>circle-ventures, coinbase-ventures, multicoin-capital, paradigm, sequoia-capital</t>
         </is>
       </c>
       <c r="M38" s="7" t="inlineStr">
@@ -22554,11 +22554,11 @@
         <v>0</v>
       </c>
       <c r="K40" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L40" s="5" t="inlineStr">
         <is>
-          <t>delphi-ventures, paradigm, robot-ventures</t>
+          <t>delphi-ventures, mechanism-capital, paradigm, robot-ventures</t>
         </is>
       </c>
       <c r="M40" s="7" t="inlineStr">
@@ -22617,11 +22617,11 @@
         <v>1</v>
       </c>
       <c r="K41" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L41" s="5" t="inlineStr">
         <is>
-          <t>lemniscap, paradigm</t>
+          <t>cmt-digital, lemniscap, paradigm</t>
         </is>
       </c>
       <c r="M41" s="7" t="inlineStr">
@@ -22865,11 +22865,11 @@
         <v>0</v>
       </c>
       <c r="K45" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L45" s="5" t="inlineStr">
         <is>
-          <t>a16z-crypto, coinbase-ventures, paradigm</t>
+          <t>a16z-crypto, coinbase-ventures, paradigm, sequoia-capital</t>
         </is>
       </c>
       <c r="M45" s="7" t="inlineStr">
@@ -23109,11 +23109,11 @@
         <v>0</v>
       </c>
       <c r="K49" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L49" s="5" t="inlineStr">
         <is>
-          <t>paradigm</t>
+          <t>gsr, paradigm, solana-ventures</t>
         </is>
       </c>
       <c r="M49" s="7" t="inlineStr">
@@ -23174,11 +23174,11 @@
         <v>1</v>
       </c>
       <c r="K50" s="6" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="L50" s="5" t="inlineStr">
         <is>
-          <t>founders-fund, paradigm</t>
+          <t>alameda-research, founders-fund, iosg-ventures, paradigm, sequoia-capital</t>
         </is>
       </c>
       <c r="M50" s="7" t="inlineStr">
@@ -23237,11 +23237,11 @@
         <v>0</v>
       </c>
       <c r="K51" s="6" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="L51" s="5" t="inlineStr">
         <is>
-          <t>multicoin-capital, paradigm</t>
+          <t>alameda-research, hack-vc, multicoin-capital, paradigm, solana-ventures</t>
         </is>
       </c>
       <c r="M51" s="7" t="inlineStr">
@@ -23426,11 +23426,11 @@
         <v>1</v>
       </c>
       <c r="K54" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L54" s="5" t="inlineStr">
         <is>
-          <t>paradigm</t>
+          <t>alliance-dao, iosg-ventures, paradigm</t>
         </is>
       </c>
       <c r="M54" s="7" t="inlineStr">
@@ -23548,11 +23548,11 @@
         <v>2</v>
       </c>
       <c r="K56" s="6" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="L56" s="5" t="inlineStr">
         <is>
-          <t>multicoin-capital, paradigm</t>
+          <t>alameda-research, animoca-brands, multicoin-capital, paradigm, solana-ventures</t>
         </is>
       </c>
       <c r="M56" s="7" t="inlineStr">
@@ -23607,11 +23607,11 @@
         <v>1</v>
       </c>
       <c r="K57" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L57" s="5" t="inlineStr">
         <is>
-          <t>paradigm</t>
+          <t>paradigm, sequoia-capital</t>
         </is>
       </c>
       <c r="M57" s="7" t="inlineStr">
@@ -23670,11 +23670,11 @@
         <v>2</v>
       </c>
       <c r="K58" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L58" s="5" t="inlineStr">
         <is>
-          <t>coinbase-ventures, paradigm</t>
+          <t>cmt-digital, coinbase-ventures, paradigm</t>
         </is>
       </c>
       <c r="M58" s="7" t="inlineStr">
@@ -23859,11 +23859,11 @@
         <v>0</v>
       </c>
       <c r="K61" s="6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L61" s="5" t="inlineStr">
         <is>
-          <t>a16z-crypto, paradigm</t>
+          <t>a16z-crypto, jump-crypto, paradigm, solana-ventures</t>
         </is>
       </c>
       <c r="M61" s="7" t="inlineStr">
@@ -23985,11 +23985,11 @@
         <v>4</v>
       </c>
       <c r="K63" s="6" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="L63" s="5" t="inlineStr">
         <is>
-          <t>paradigm</t>
+          <t>borderless-capital, gsr, jump-crypto, mirana-ventures, paradigm</t>
         </is>
       </c>
       <c r="M63" s="7" t="inlineStr">
@@ -24048,11 +24048,11 @@
         <v>0</v>
       </c>
       <c r="K64" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L64" s="5" t="inlineStr">
         <is>
-          <t>paradigm, robot-ventures</t>
+          <t>alameda-research, paradigm, robot-ventures</t>
         </is>
       </c>
       <c r="M64" s="7" t="inlineStr">
@@ -24174,11 +24174,11 @@
         <v>0</v>
       </c>
       <c r="K66" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L66" s="5" t="inlineStr">
         <is>
-          <t>paradigm</t>
+          <t>paradigm, sequoia-capital</t>
         </is>
       </c>
       <c r="M66" s="7" t="inlineStr">
@@ -24424,11 +24424,11 @@
         <v>2</v>
       </c>
       <c r="K70" s="6" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="L70" s="5" t="inlineStr">
         <is>
-          <t>a16z-crypto, coinbase-ventures, multicoin-capital, paradigm</t>
+          <t>a16z-crypto, animoca-brands, coinbase-ventures, multicoin-capital, paradigm, solana-ventures</t>
         </is>
       </c>
       <c r="M70" s="7" t="inlineStr">
@@ -24487,11 +24487,11 @@
         <v>1</v>
       </c>
       <c r="K71" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L71" s="5" t="inlineStr">
         <is>
-          <t>a16z-crypto, paradigm</t>
+          <t>a16z-crypto, animoca-brands, paradigm</t>
         </is>
       </c>
       <c r="M71" s="7" t="inlineStr">
@@ -24546,11 +24546,11 @@
         <v>0</v>
       </c>
       <c r="K72" s="6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L72" s="5" t="inlineStr">
         <is>
-          <t>a16z-crypto, paradigm</t>
+          <t>a16z-crypto, animoca-brands, paradigm, yzi-labs</t>
         </is>
       </c>
       <c r="M72" s="7" t="inlineStr">
@@ -24672,11 +24672,11 @@
         <v>0</v>
       </c>
       <c r="K74" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L74" s="5" t="inlineStr">
         <is>
-          <t>paradigm</t>
+          <t>animoca-brands, jump-crypto, paradigm</t>
         </is>
       </c>
       <c r="M74" s="7" t="inlineStr">
@@ -24920,11 +24920,11 @@
         <v>2</v>
       </c>
       <c r="K78" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L78" s="5" t="inlineStr">
         <is>
-          <t>paradigm</t>
+          <t>paradigm, sequoia-capital</t>
         </is>
       </c>
       <c r="M78" s="7" t="inlineStr">
@@ -25046,11 +25046,11 @@
         <v>0</v>
       </c>
       <c r="K80" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L80" s="5" t="inlineStr">
         <is>
-          <t>coinbase-ventures, paradigm</t>
+          <t>circle-ventures, coinbase-ventures, paradigm</t>
         </is>
       </c>
       <c r="M80" s="7" t="inlineStr">
@@ -25172,11 +25172,11 @@
         <v>0</v>
       </c>
       <c r="K82" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L82" s="5" t="inlineStr">
         <is>
-          <t>electric-capital, paradigm</t>
+          <t>electric-capital, paradigm, sequoia-capital</t>
         </is>
       </c>
       <c r="M82" s="7" t="inlineStr">
@@ -25296,11 +25296,11 @@
         <v>1</v>
       </c>
       <c r="K84" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L84" s="5" t="inlineStr">
         <is>
-          <t>paradigm</t>
+          <t>hashkey-capital, paradigm</t>
         </is>
       </c>
       <c r="M84" s="7" t="inlineStr">
@@ -25481,11 +25481,11 @@
         <v>1</v>
       </c>
       <c r="K87" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L87" s="5" t="inlineStr">
         <is>
-          <t>dragonfly, paradigm</t>
+          <t>dragonfly, hypersphere, paradigm</t>
         </is>
       </c>
       <c r="M87" s="7" t="inlineStr">
@@ -25544,11 +25544,11 @@
         <v>1</v>
       </c>
       <c r="K88" s="6" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="L88" s="5" t="inlineStr">
         <is>
-          <t>haun-ventures, paradigm, robot-ventures</t>
+          <t>circle-ventures, haun-ventures, paradigm, polygon-ventures, robot-ventures, solana-ventures</t>
         </is>
       </c>
       <c r="M88" s="7" t="inlineStr">
@@ -25607,11 +25607,11 @@
         <v>0</v>
       </c>
       <c r="K89" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L89" s="5" t="inlineStr">
         <is>
-          <t>coinbase-ventures, paradigm</t>
+          <t>coinbase-ventures, paradigm, sequoia-capital</t>
         </is>
       </c>
       <c r="M89" s="7" t="inlineStr">
@@ -25798,11 +25798,11 @@
         <v>2</v>
       </c>
       <c r="K92" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L92" s="5" t="inlineStr">
         <is>
-          <t>bain-capital-crypto, paradigm, robot-ventures</t>
+          <t>bain-capital-crypto, jump-crypto, paradigm, robot-ventures</t>
         </is>
       </c>
       <c r="M92" s="7" t="inlineStr">
@@ -26168,11 +26168,11 @@
         <v>1</v>
       </c>
       <c r="K98" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L98" s="5" t="inlineStr">
         <is>
-          <t>paradigm</t>
+          <t>paradigm, sequoia-capital</t>
         </is>
       </c>
       <c r="M98" s="7" t="inlineStr">
@@ -26601,11 +26601,11 @@
         <v>1</v>
       </c>
       <c r="K105" s="6" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="L105" s="5" t="inlineStr">
         <is>
-          <t>paradigm, polychain</t>
+          <t>amber-group, galaxy-digital, hack-vc, hashkey-capital, huobi-ventures, iosg-ventures, paradigm, polychain</t>
         </is>
       </c>
       <c r="M105" s="7" t="inlineStr">
@@ -27032,11 +27032,11 @@
         <v>1</v>
       </c>
       <c r="K112" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L112" s="5" t="inlineStr">
         <is>
-          <t>paradigm, polychain</t>
+          <t>foresight-ventures, paradigm, polychain</t>
         </is>
       </c>
       <c r="M112" s="7" t="inlineStr">
@@ -27095,11 +27095,11 @@
         <v>2</v>
       </c>
       <c r="K113" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L113" s="5" t="inlineStr">
         <is>
-          <t>bain-capital-crypto, paradigm, robot-ventures</t>
+          <t>bain-capital-crypto, fenbushi-capital, paradigm, robot-ventures</t>
         </is>
       </c>
       <c r="M113" s="7" t="inlineStr">
@@ -27160,11 +27160,11 @@
         <v>2</v>
       </c>
       <c r="K114" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L114" s="5" t="inlineStr">
         <is>
-          <t>a16z-crypto, paradigm</t>
+          <t>a16z-crypto, paradigm, sequoia-capital</t>
         </is>
       </c>
       <c r="M114" s="7" t="inlineStr">
@@ -27400,11 +27400,11 @@
         <v>1</v>
       </c>
       <c r="K118" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L118" s="5" t="inlineStr">
         <is>
-          <t>paradigm</t>
+          <t>paradigm, sequoia-capital</t>
         </is>
       </c>
       <c r="M118" s="7" t="inlineStr">
@@ -27656,11 +27656,11 @@
         <v>1</v>
       </c>
       <c r="K122" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L122" s="5" t="inlineStr">
         <is>
-          <t>multicoin-capital, paradigm</t>
+          <t>multicoin-capital, paradigm, sequoia-capital</t>
         </is>
       </c>
       <c r="M122" s="7" t="inlineStr">
@@ -28150,11 +28150,11 @@
         <v>0</v>
       </c>
       <c r="K130" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L130" s="5" t="inlineStr">
         <is>
-          <t>a16z-crypto, coinbase-ventures, paradigm</t>
+          <t>a16z-crypto, coinbase-ventures, paradigm, sequoia-capital</t>
         </is>
       </c>
       <c r="M130" s="7" t="inlineStr">
@@ -28274,11 +28274,11 @@
         <v>2</v>
       </c>
       <c r="K132" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L132" s="5" t="inlineStr">
         <is>
-          <t>a16z-crypto, paradigm</t>
+          <t>a16z-crypto, paradigm, sequoia-capital</t>
         </is>
       </c>
       <c r="M132" s="7" t="inlineStr">
@@ -28518,11 +28518,11 @@
         <v>0</v>
       </c>
       <c r="K136" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L136" s="5" t="inlineStr">
         <is>
-          <t>paradigm</t>
+          <t>hack-vc, paradigm</t>
         </is>
       </c>
       <c r="M136" s="7" t="inlineStr">
@@ -28711,11 +28711,11 @@
         <v>1</v>
       </c>
       <c r="K139" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L139" s="5" t="inlineStr">
         <is>
-          <t>figment-capital, paradigm</t>
+          <t>figment-capital, gsr, paradigm</t>
         </is>
       </c>
       <c r="M139" s="7" t="inlineStr">
@@ -28776,11 +28776,11 @@
         <v>1</v>
       </c>
       <c r="K140" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L140" s="5" t="inlineStr">
         <is>
-          <t>a16z-crypto, paradigm</t>
+          <t>a16z-crypto, paradigm, sequoia-capital</t>
         </is>
       </c>
       <c r="M140" s="7" t="inlineStr">
@@ -28961,11 +28961,11 @@
         <v>3</v>
       </c>
       <c r="K143" s="6" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="L143" s="5" t="inlineStr">
         <is>
-          <t>a16z-crypto, paradigm</t>
+          <t>a16z-crypto, circle-ventures, hashkey-capital, iosg-ventures, mirana-ventures, paradigm</t>
         </is>
       </c>
       <c r="M143" s="7" t="inlineStr">
@@ -35467,7 +35467,7 @@
       </c>
       <c r="F2" s="12" t="inlineStr">
         <is>
-          <t>Fondspagina toont een vast maximum aantal regels; dit is een displaylimiet en geen portefeuilletotaal.</t>
+          <t>The fund page shows a fixed maximum number of rows; this is a display limit, not a portfolio total.</t>
         </is>
       </c>
       <c r="G2" s="6" t="n">
@@ -35475,13 +35475,13 @@
       </c>
       <c r="H2" s="12" t="inlineStr">
         <is>
-          <t>Unieke uitgaande domeinen als benadering van portefeuillenamen.</t>
+          <t>Unique outbound domains as an approximation of portfolio names.</t>
         </is>
       </c>
       <c r="I2" s="6" t="n"/>
       <c r="J2" s="12" t="inlineStr">
         <is>
-          <t>Geen telling verkregen; niet geschat.</t>
+          <t>No count obtained; not estimated.</t>
         </is>
       </c>
       <c r="K2" s="6" t="n">
@@ -35489,7 +35489,7 @@
       </c>
       <c r="L2" s="12" t="inlineStr">
         <is>
-          <t>`investments` is CryptoRanks eigen telling. De zichtbare portefeuillelijst toont zonder account maar tien regels; die lijst is niet gebruikt.</t>
+          <t>`investments` is CryptoRank's own count. The visible portfolio list shows only ten rows without an account; that list was not used.</t>
         </is>
       </c>
       <c r="M2" s="6" t="n">
